--- a/Графики.xlsx
+++ b/Графики.xlsx
@@ -8,178 +8,55 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nikit\Desktop\semester_work\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{79B44AAB-5042-4960-ADC4-F7C82CCC8A48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2AF1EB98-E80D-466C-BDB1-3525BF01D2D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{42875BCE-94AA-44F5-8329-5CC7100793A4}"/>
   </bookViews>
   <sheets>
-    <sheet name="results" sheetId="1" r:id="rId1"/>
+    <sheet name="Графики Зависимости" sheetId="1" r:id="rId1"/>
+    <sheet name="Теоретическая сложность" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
   <si>
-    <t>Vertices,Time,Iterations</t>
+    <t>Размер графа (V)</t>
   </si>
   <si>
-    <t>100,3.55600262992084e-05,484</t>
+    <t>Время выполнения (сек)</t>
   </si>
   <si>
-    <t>300,0.0003000000026077032,2694</t>
+    <t>Количество итераций</t>
   </si>
   <si>
-    <t>500,0.0006879199994727969,6492</t>
+    <t>Теоретическая Сложность</t>
   </si>
   <si>
-    <t>700,0.000609240005724132,11847</t>
-  </si>
-  <si>
-    <t>900,0.000901239993982017,19145</t>
-  </si>
-  <si>
-    <t>1100,0.0013728799996897579,27215</t>
-  </si>
-  <si>
-    <t>1300,0.0017525199917145073,37736</t>
-  </si>
-  <si>
-    <t>1500,0.002582119998987764,49544</t>
-  </si>
-  <si>
-    <t>1700,0.006460879999212921,63268</t>
-  </si>
-  <si>
-    <t>1900,0.006728740001562983,78089</t>
-  </si>
-  <si>
-    <t>2100,0.009499459993094206,94468</t>
-  </si>
-  <si>
-    <t>2300,0.005224160000216216,112450</t>
-  </si>
-  <si>
-    <t>2500,0.006551920005585998,132303</t>
-  </si>
-  <si>
-    <t>2700,0.01230312001425773,154543</t>
-  </si>
-  <si>
-    <t>2900,0.01926612000679597,177082</t>
-  </si>
-  <si>
-    <t>3100,0.018957060005050153,202057</t>
-  </si>
-  <si>
-    <t>3300,0.02101478000404313,228049</t>
-  </si>
-  <si>
-    <t>3500,0.026813780004158617,255838</t>
-  </si>
-  <si>
-    <t>3700,0.02969733999343589,285391</t>
-  </si>
-  <si>
-    <t>3900,0.034103799995500596,318014</t>
-  </si>
-  <si>
-    <t>4100,0.03723813999677077,349271</t>
-  </si>
-  <si>
-    <t>4300,0.040905919997021555,383572</t>
-  </si>
-  <si>
-    <t>4500,0.04303081999532878,419354</t>
-  </si>
-  <si>
-    <t>4700,0.029055580007843675,455017</t>
-  </si>
-  <si>
-    <t>4900,0.051388479990419,494703</t>
-  </si>
-  <si>
-    <t>5100,0.05552488003158942,534469</t>
-  </si>
-  <si>
-    <t>5300,0.057488699990790336,578279</t>
-  </si>
-  <si>
-    <t>5500,0.06523487999802455,621329</t>
-  </si>
-  <si>
-    <t>5700,0.06905398000963033,665175</t>
-  </si>
-  <si>
-    <t>5900,0.07489688001805916,712886</t>
-  </si>
-  <si>
-    <t>6100,0.08002720000222326,759619</t>
-  </si>
-  <si>
-    <t>6300,0.08598383999196813,812546</t>
-  </si>
-  <si>
-    <t>6500,0.09149878000607714,863606</t>
-  </si>
-  <si>
-    <t>6700,0.0965263800113462,917533</t>
-  </si>
-  <si>
-    <t>6900,0.10375804000068456,972079</t>
-  </si>
-  <si>
-    <t>7100,0.10243351999670267,1027181</t>
-  </si>
-  <si>
-    <t>7300,0.11449620000785217,1087236</t>
-  </si>
-  <si>
-    <t>7500,0.11453254000516608,1149507</t>
-  </si>
-  <si>
-    <t>7700,0.12662527998909354,1211949</t>
-  </si>
-  <si>
-    <t>7900,0.13229890001239256,1271159</t>
-  </si>
-  <si>
-    <t>8100,0.1398407000117004,1336629</t>
-  </si>
-  <si>
-    <t>8300,0.1480320599861443,1402884</t>
-  </si>
-  <si>
-    <t>8500,0.1541800400125794,1471282</t>
-  </si>
-  <si>
-    <t>8700,0.13695156000321732,1542017</t>
-  </si>
-  <si>
-    <t>8900,0.15430830001132562,1612898</t>
-  </si>
-  <si>
-    <t>9100,0.17326336000114678,1684489</t>
-  </si>
-  <si>
-    <t>9300,0.18431028000777588,1759271</t>
-  </si>
-  <si>
-    <t>9500,0.19325944000156597,1833777</t>
-  </si>
-  <si>
-    <t>9700,0.19938160000601785,1911227</t>
-  </si>
-  <si>
-    <t>9900,0.20350204000715166,1991307</t>
+    <t>Экспериментальные итерации</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -332,8 +209,24 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -513,8 +406,14 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -629,6 +528,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -674,8 +588,20 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% — акцент1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -732,6 +658,4065 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Графики Зависимости'!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Время выполнения (сек)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="9525" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="6"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent6">
+                      <a:satMod val="103000"/>
+                      <a:lumMod val="102000"/>
+                      <a:tint val="94000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="50000">
+                    <a:schemeClr val="accent6">
+                      <a:satMod val="110000"/>
+                      <a:lumMod val="100000"/>
+                      <a:shade val="100000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent6">
+                      <a:lumMod val="99000"/>
+                      <a:satMod val="120000"/>
+                      <a:shade val="78000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent6"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="63000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Графики Зависимости'!$A$2:$A$51</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="50"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>700</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>900</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1100</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1300</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1500</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1700</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1900</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2100</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2300</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2500</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2700</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2900</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3100</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3300</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3500</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3700</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>3900</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>4100</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>4300</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>4500</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>4700</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>4900</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>5100</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>5300</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>5500</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>5700</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>5900</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>6100</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>6300</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>6500</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>6700</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>6900</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>7100</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>7300</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>7500</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>7700</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>7900</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>8100</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>8300</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>8500</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>8700</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>8900</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>9100</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>9300</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>9500</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>9700</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>9900</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Графики Зависимости'!$B$2:$B$51</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="50"/>
+                <c:pt idx="0" formatCode="0.00E+00">
+                  <c:v>3.5560026299208401E-5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.0000000260770298E-4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6.8791999947279603E-4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.0924000572413204E-4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9.01239993982017E-4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.3728799996897501E-3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.7525199917144999E-3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.58211999898776E-3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6.46087999921292E-3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>6.7287400015629802E-3</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>9.4994599930942007E-3</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>5.2241600002162101E-3</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>6.5519200055859901E-3</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.23031200142577E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.9266120006795898E-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.89570600050501E-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2.1014780004043099E-2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2.6813780004158599E-2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2.9697339993435799E-2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>3.4103799995500499E-2</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>3.7238139996770697E-2</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>4.0905919997021499E-2</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>4.3030819995328699E-2</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2.9055580007843598E-2</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>5.1388479990418998E-2</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>5.5524880031589403E-2</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>5.7488699990790301E-2</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>6.5234879998024506E-2</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>6.9053980009630297E-2</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>7.4896880018059095E-2</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>8.0027200002223201E-2</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>8.5983839991968097E-2</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>9.1498780006077099E-2</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>9.6526380011346197E-2</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.103758040000684</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.102433519996702</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.114496200007852</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.11453254000516599</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.12662527998909301</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.132298900012392</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.13984070001169999</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.14803205998614399</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.15418004001257901</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.13695156000321701</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.15430830001132501</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.17326336000114601</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.184310280007775</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.193259440001565</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.19938160000601701</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.203502040007151</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-B1A1-4E98-83F2-114E6B22271A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1881404863"/>
+        <c:axId val="1881412063"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1881404863"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1881412063"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1881412063"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00E+00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1881404863"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Графики Зависимости'!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Количество итераций</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="9525" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="6"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent6">
+                      <a:satMod val="103000"/>
+                      <a:lumMod val="102000"/>
+                      <a:tint val="94000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="50000">
+                    <a:schemeClr val="accent6">
+                      <a:satMod val="110000"/>
+                      <a:lumMod val="100000"/>
+                      <a:shade val="100000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent6">
+                      <a:lumMod val="99000"/>
+                      <a:satMod val="120000"/>
+                      <a:shade val="78000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent6"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="63000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Графики Зависимости'!$A$2:$A$51</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="50"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>700</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>900</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1100</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1300</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1500</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1700</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1900</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2100</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2300</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2500</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2700</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2900</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3100</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3300</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3500</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3700</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>3900</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>4100</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>4300</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>4500</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>4700</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>4900</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>5100</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>5300</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>5500</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>5700</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>5900</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>6100</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>6300</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>6500</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>6700</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>6900</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>7100</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>7300</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>7500</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>7700</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>7900</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>8100</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>8300</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>8500</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>8700</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>8900</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>9100</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>9300</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>9500</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>9700</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>9900</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Графики Зависимости'!$C$2:$C$51</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="50"/>
+                <c:pt idx="0">
+                  <c:v>484</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2694</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6492</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>11847</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19145</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>27215</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>37736</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>49544</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>63268</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>78089</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>94468</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>112450</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>132303</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>154543</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>177082</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>202057</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>228049</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>255838</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>285391</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>318014</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>349271</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>383572</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>419354</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>455017</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>494703</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>534469</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>578279</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>621329</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>665175</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>712886</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>759619</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>812546</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>863606</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>917533</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>972079</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>1027181</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>1087236</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>1149507</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>1211949</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>1271159</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>1336629</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>1402884</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>1471282</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>1542017</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>1612898</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>1684489</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>1759271</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>1833777</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>1911227</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>1991307</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-6E17-40C7-A605-E8F3A8CCB1E0}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1834401375"/>
+        <c:axId val="1834402815"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1834401375"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1834402815"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1834402815"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1834401375"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
+              <a:t>Сравнение экспериментальной и теоретической сложности алгоритма</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Теоретическая сложность'!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Теоретическая Сложность</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="9525" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="6"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent6">
+                      <a:satMod val="103000"/>
+                      <a:lumMod val="102000"/>
+                      <a:tint val="94000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="50000">
+                    <a:schemeClr val="accent6">
+                      <a:satMod val="110000"/>
+                      <a:lumMod val="100000"/>
+                      <a:shade val="100000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent6">
+                      <a:lumMod val="99000"/>
+                      <a:satMod val="120000"/>
+                      <a:shade val="78000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent6"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="63000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Теоретическая сложность'!$A$2:$A$51</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="50"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>700</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>900</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1100</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1300</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1500</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1700</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1900</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2100</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2300</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2500</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2700</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2900</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3100</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3300</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3500</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3700</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>3900</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>4100</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>4300</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>4500</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>4700</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>4900</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>5100</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>5300</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>5500</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>5700</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>5900</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>6100</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>6300</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>6500</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>6700</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>6900</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>7100</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>7300</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>7500</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>7700</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>7900</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>8100</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>8300</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>8500</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>8700</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>8900</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>9100</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>9300</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>9500</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>9700</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>9900</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Теоретическая сложность'!$B$2:$B$51</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="50"/>
+                <c:pt idx="0">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1800</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9800</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>16200</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>24200</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>33800</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>45000</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>57800</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>72200</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>88200</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>105800</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>125000</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>145800</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>168200</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>192200</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>217800</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>245000</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>273800</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>304200</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>336200</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>369800</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>405000</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>441800</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>480200</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>520200</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>561800</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>605000</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>649800</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>696200</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>744200</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>793800</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>845000</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>897800</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>952200</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>1008200</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>1065800</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>1125000</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>1185800</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>1248200</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>1312200</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>1377800</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>1445000</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>1513800</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>1584200</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>1656200</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>1729800</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>1805000</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>1881800</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>1960200</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-A41B-4F49-BD4C-8F5E30F5D330}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Теоретическая сложность'!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Экспериментальные итерации</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="9525" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="6"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent5">
+                      <a:satMod val="103000"/>
+                      <a:lumMod val="102000"/>
+                      <a:tint val="94000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="50000">
+                    <a:schemeClr val="accent5">
+                      <a:satMod val="110000"/>
+                      <a:lumMod val="100000"/>
+                      <a:shade val="100000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent5">
+                      <a:lumMod val="99000"/>
+                      <a:satMod val="120000"/>
+                      <a:shade val="78000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent5"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="63000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Теоретическая сложность'!$A$2:$A$51</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="50"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>700</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>900</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1100</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1300</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1500</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1700</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1900</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2100</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2300</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2500</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2700</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2900</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3100</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3300</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3500</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3700</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>3900</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>4100</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>4300</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>4500</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>4700</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>4900</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>5100</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>5300</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>5500</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>5700</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>5900</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>6100</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>6300</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>6500</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>6700</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>6900</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>7100</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>7300</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>7500</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>7700</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>7900</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>8100</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>8300</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>8500</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>8700</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>8900</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>9100</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>9300</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>9500</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>9700</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>9900</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Теоретическая сложность'!$C$2:$C$51</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="50"/>
+                <c:pt idx="0">
+                  <c:v>484</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2694</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6492</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>11847</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19145</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>27215</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>37736</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>49544</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>63268</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>78089</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>94468</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>112450</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>132303</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>154543</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>177082</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>202057</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>228049</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>255838</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>285391</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>318014</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>349271</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>383572</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>419354</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>455017</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>494703</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>534469</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>578279</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>621329</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>665175</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>712886</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>759619</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>812546</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>863606</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>917533</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>972079</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>1027181</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>1087236</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>1149507</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>1211949</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>1271159</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>1336629</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>1402884</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>1471282</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>1542017</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>1612898</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>1684489</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>1759271</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>1833777</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>1911227</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>1991307</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-A41B-4F49-BD4C-8F5E30F5D330}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1662790239"/>
+        <c:axId val="1662783039"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1662790239"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1662783039"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1662783039"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1662790239"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="13">
+  <a:schemeClr val="accent6"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent4"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="13">
+  <a:schemeClr val="accent6"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent4"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="13">
+  <a:schemeClr val="accent6"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent4"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="343">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="343">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="343">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>20028</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>6926</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>3727</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Диаграмма 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{839A4988-80D8-0CE7-4AEF-5C024FB210BB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>608771</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>8283</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>189258</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Диаграмма 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8D3952A3-6E8E-FFA1-CEA2-6FBD1944DA29}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>8283</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>8282</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Диаграмма 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{56C07EA0-340B-68E1-CE29-488CCCB3F92D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1051,265 +5036,1203 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6381B384-DDC2-4A38-8B92-A87B9FDA61FD}">
-  <dimension ref="A1:A51"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="3" width="28.7109375" style="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>50</v>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>100</v>
+      </c>
+      <c r="B2" s="4">
+        <v>3.5560026299208401E-5</v>
+      </c>
+      <c r="C2" s="2">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>300</v>
+      </c>
+      <c r="B3" s="2">
+        <v>3.0000000260770298E-4</v>
+      </c>
+      <c r="C3" s="2">
+        <v>2694</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>500</v>
+      </c>
+      <c r="B4" s="2">
+        <v>6.8791999947279603E-4</v>
+      </c>
+      <c r="C4" s="2">
+        <v>6492</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>700</v>
+      </c>
+      <c r="B5" s="2">
+        <v>6.0924000572413204E-4</v>
+      </c>
+      <c r="C5" s="2">
+        <v>11847</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>900</v>
+      </c>
+      <c r="B6" s="2">
+        <v>9.01239993982017E-4</v>
+      </c>
+      <c r="C6" s="2">
+        <v>19145</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>1100</v>
+      </c>
+      <c r="B7" s="2">
+        <v>1.3728799996897501E-3</v>
+      </c>
+      <c r="C7" s="2">
+        <v>27215</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>1300</v>
+      </c>
+      <c r="B8" s="2">
+        <v>1.7525199917144999E-3</v>
+      </c>
+      <c r="C8" s="2">
+        <v>37736</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>1500</v>
+      </c>
+      <c r="B9" s="2">
+        <v>2.58211999898776E-3</v>
+      </c>
+      <c r="C9" s="2">
+        <v>49544</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>1700</v>
+      </c>
+      <c r="B10" s="2">
+        <v>6.46087999921292E-3</v>
+      </c>
+      <c r="C10" s="2">
+        <v>63268</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>1900</v>
+      </c>
+      <c r="B11" s="2">
+        <v>6.7287400015629802E-3</v>
+      </c>
+      <c r="C11" s="2">
+        <v>78089</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>2100</v>
+      </c>
+      <c r="B12" s="2">
+        <v>9.4994599930942007E-3</v>
+      </c>
+      <c r="C12" s="2">
+        <v>94468</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>2300</v>
+      </c>
+      <c r="B13" s="2">
+        <v>5.2241600002162101E-3</v>
+      </c>
+      <c r="C13" s="2">
+        <v>112450</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>2500</v>
+      </c>
+      <c r="B14" s="2">
+        <v>6.5519200055859901E-3</v>
+      </c>
+      <c r="C14" s="2">
+        <v>132303</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>2700</v>
+      </c>
+      <c r="B15" s="2">
+        <v>1.23031200142577E-2</v>
+      </c>
+      <c r="C15" s="2">
+        <v>154543</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>2900</v>
+      </c>
+      <c r="B16" s="2">
+        <v>1.9266120006795898E-2</v>
+      </c>
+      <c r="C16" s="2">
+        <v>177082</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>3100</v>
+      </c>
+      <c r="B17" s="2">
+        <v>1.89570600050501E-2</v>
+      </c>
+      <c r="C17" s="2">
+        <v>202057</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>3300</v>
+      </c>
+      <c r="B18" s="2">
+        <v>2.1014780004043099E-2</v>
+      </c>
+      <c r="C18" s="2">
+        <v>228049</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <v>3500</v>
+      </c>
+      <c r="B19" s="2">
+        <v>2.6813780004158599E-2</v>
+      </c>
+      <c r="C19" s="2">
+        <v>255838</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>3700</v>
+      </c>
+      <c r="B20" s="2">
+        <v>2.9697339993435799E-2</v>
+      </c>
+      <c r="C20" s="2">
+        <v>285391</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
+        <v>3900</v>
+      </c>
+      <c r="B21" s="2">
+        <v>3.4103799995500499E-2</v>
+      </c>
+      <c r="C21" s="2">
+        <v>318014</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
+        <v>4100</v>
+      </c>
+      <c r="B22" s="2">
+        <v>3.7238139996770697E-2</v>
+      </c>
+      <c r="C22" s="2">
+        <v>349271</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="2">
+        <v>4300</v>
+      </c>
+      <c r="B23" s="2">
+        <v>4.0905919997021499E-2</v>
+      </c>
+      <c r="C23" s="2">
+        <v>383572</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
+        <v>4500</v>
+      </c>
+      <c r="B24" s="2">
+        <v>4.3030819995328699E-2</v>
+      </c>
+      <c r="C24" s="2">
+        <v>419354</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="2">
+        <v>4700</v>
+      </c>
+      <c r="B25" s="2">
+        <v>2.9055580007843598E-2</v>
+      </c>
+      <c r="C25" s="2">
+        <v>455017</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
+        <v>4900</v>
+      </c>
+      <c r="B26" s="2">
+        <v>5.1388479990418998E-2</v>
+      </c>
+      <c r="C26" s="2">
+        <v>494703</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
+        <v>5100</v>
+      </c>
+      <c r="B27" s="2">
+        <v>5.5524880031589403E-2</v>
+      </c>
+      <c r="C27" s="2">
+        <v>534469</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
+        <v>5300</v>
+      </c>
+      <c r="B28" s="2">
+        <v>5.7488699990790301E-2</v>
+      </c>
+      <c r="C28" s="2">
+        <v>578279</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="2">
+        <v>5500</v>
+      </c>
+      <c r="B29" s="2">
+        <v>6.5234879998024506E-2</v>
+      </c>
+      <c r="C29" s="2">
+        <v>621329</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
+        <v>5700</v>
+      </c>
+      <c r="B30" s="2">
+        <v>6.9053980009630297E-2</v>
+      </c>
+      <c r="C30" s="2">
+        <v>665175</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
+        <v>5900</v>
+      </c>
+      <c r="B31" s="2">
+        <v>7.4896880018059095E-2</v>
+      </c>
+      <c r="C31" s="2">
+        <v>712886</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
+        <v>6100</v>
+      </c>
+      <c r="B32" s="2">
+        <v>8.0027200002223201E-2</v>
+      </c>
+      <c r="C32" s="2">
+        <v>759619</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
+        <v>6300</v>
+      </c>
+      <c r="B33" s="2">
+        <v>8.5983839991968097E-2</v>
+      </c>
+      <c r="C33" s="2">
+        <v>812546</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
+        <v>6500</v>
+      </c>
+      <c r="B34" s="2">
+        <v>9.1498780006077099E-2</v>
+      </c>
+      <c r="C34" s="2">
+        <v>863606</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="2">
+        <v>6700</v>
+      </c>
+      <c r="B35" s="2">
+        <v>9.6526380011346197E-2</v>
+      </c>
+      <c r="C35" s="2">
+        <v>917533</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
+        <v>6900</v>
+      </c>
+      <c r="B36" s="2">
+        <v>0.103758040000684</v>
+      </c>
+      <c r="C36" s="2">
+        <v>972079</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="2">
+        <v>7100</v>
+      </c>
+      <c r="B37" s="2">
+        <v>0.102433519996702</v>
+      </c>
+      <c r="C37" s="2">
+        <v>1027181</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="2">
+        <v>7300</v>
+      </c>
+      <c r="B38" s="2">
+        <v>0.114496200007852</v>
+      </c>
+      <c r="C38" s="2">
+        <v>1087236</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="2">
+        <v>7500</v>
+      </c>
+      <c r="B39" s="2">
+        <v>0.11453254000516599</v>
+      </c>
+      <c r="C39" s="2">
+        <v>1149507</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="2">
+        <v>7700</v>
+      </c>
+      <c r="B40" s="2">
+        <v>0.12662527998909301</v>
+      </c>
+      <c r="C40" s="2">
+        <v>1211949</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="2">
+        <v>7900</v>
+      </c>
+      <c r="B41" s="2">
+        <v>0.132298900012392</v>
+      </c>
+      <c r="C41" s="2">
+        <v>1271159</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="2">
+        <v>8100</v>
+      </c>
+      <c r="B42" s="2">
+        <v>0.13984070001169999</v>
+      </c>
+      <c r="C42" s="2">
+        <v>1336629</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="2">
+        <v>8300</v>
+      </c>
+      <c r="B43" s="2">
+        <v>0.14803205998614399</v>
+      </c>
+      <c r="C43" s="2">
+        <v>1402884</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="2">
+        <v>8500</v>
+      </c>
+      <c r="B44" s="2">
+        <v>0.15418004001257901</v>
+      </c>
+      <c r="C44" s="2">
+        <v>1471282</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="2">
+        <v>8700</v>
+      </c>
+      <c r="B45" s="2">
+        <v>0.13695156000321701</v>
+      </c>
+      <c r="C45" s="2">
+        <v>1542017</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="2">
+        <v>8900</v>
+      </c>
+      <c r="B46" s="2">
+        <v>0.15430830001132501</v>
+      </c>
+      <c r="C46" s="2">
+        <v>1612898</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="2">
+        <v>9100</v>
+      </c>
+      <c r="B47" s="2">
+        <v>0.17326336000114601</v>
+      </c>
+      <c r="C47" s="2">
+        <v>1684489</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="2">
+        <v>9300</v>
+      </c>
+      <c r="B48" s="2">
+        <v>0.184310280007775</v>
+      </c>
+      <c r="C48" s="2">
+        <v>1759271</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="2">
+        <v>9500</v>
+      </c>
+      <c r="B49" s="2">
+        <v>0.193259440001565</v>
+      </c>
+      <c r="C49" s="2">
+        <v>1833777</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="2">
+        <v>9700</v>
+      </c>
+      <c r="B50" s="2">
+        <v>0.19938160000601701</v>
+      </c>
+      <c r="C50" s="2">
+        <v>1911227</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="2">
+        <v>9900</v>
+      </c>
+      <c r="B51" s="2">
+        <v>0.203502040007151</v>
+      </c>
+      <c r="C51" s="2">
+        <v>1991307</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F9A124B-D074-4D74-9803-C56BADE74561}">
+  <dimension ref="A1:C51"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="33.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="33.7109375" customWidth="1"/>
+    <col min="3" max="3" width="33.7109375" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>100</v>
+      </c>
+      <c r="B2" s="2">
+        <f>A2*A2*0.02</f>
+        <v>200</v>
+      </c>
+      <c r="C2" s="2">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>300</v>
+      </c>
+      <c r="B3" s="2">
+        <f t="shared" ref="B3:B51" si="0">A3*A3*0.02</f>
+        <v>1800</v>
+      </c>
+      <c r="C3" s="2">
+        <v>2694</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>500</v>
+      </c>
+      <c r="B4" s="2">
+        <f t="shared" si="0"/>
+        <v>5000</v>
+      </c>
+      <c r="C4" s="2">
+        <v>6492</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>700</v>
+      </c>
+      <c r="B5" s="2">
+        <f t="shared" si="0"/>
+        <v>9800</v>
+      </c>
+      <c r="C5" s="2">
+        <v>11847</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>900</v>
+      </c>
+      <c r="B6" s="2">
+        <f t="shared" si="0"/>
+        <v>16200</v>
+      </c>
+      <c r="C6" s="2">
+        <v>19145</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>1100</v>
+      </c>
+      <c r="B7" s="2">
+        <f t="shared" si="0"/>
+        <v>24200</v>
+      </c>
+      <c r="C7" s="2">
+        <v>27215</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>1300</v>
+      </c>
+      <c r="B8" s="2">
+        <f t="shared" si="0"/>
+        <v>33800</v>
+      </c>
+      <c r="C8" s="2">
+        <v>37736</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>1500</v>
+      </c>
+      <c r="B9" s="2">
+        <f t="shared" si="0"/>
+        <v>45000</v>
+      </c>
+      <c r="C9" s="2">
+        <v>49544</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>1700</v>
+      </c>
+      <c r="B10" s="2">
+        <f t="shared" si="0"/>
+        <v>57800</v>
+      </c>
+      <c r="C10" s="2">
+        <v>63268</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>1900</v>
+      </c>
+      <c r="B11" s="2">
+        <f t="shared" si="0"/>
+        <v>72200</v>
+      </c>
+      <c r="C11" s="2">
+        <v>78089</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>2100</v>
+      </c>
+      <c r="B12" s="2">
+        <f t="shared" si="0"/>
+        <v>88200</v>
+      </c>
+      <c r="C12" s="2">
+        <v>94468</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>2300</v>
+      </c>
+      <c r="B13" s="2">
+        <f t="shared" si="0"/>
+        <v>105800</v>
+      </c>
+      <c r="C13" s="2">
+        <v>112450</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>2500</v>
+      </c>
+      <c r="B14" s="2">
+        <f t="shared" si="0"/>
+        <v>125000</v>
+      </c>
+      <c r="C14" s="2">
+        <v>132303</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>2700</v>
+      </c>
+      <c r="B15" s="2">
+        <f t="shared" si="0"/>
+        <v>145800</v>
+      </c>
+      <c r="C15" s="2">
+        <v>154543</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>2900</v>
+      </c>
+      <c r="B16" s="2">
+        <f t="shared" si="0"/>
+        <v>168200</v>
+      </c>
+      <c r="C16" s="2">
+        <v>177082</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>3100</v>
+      </c>
+      <c r="B17" s="2">
+        <f t="shared" si="0"/>
+        <v>192200</v>
+      </c>
+      <c r="C17" s="2">
+        <v>202057</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>3300</v>
+      </c>
+      <c r="B18" s="2">
+        <f t="shared" si="0"/>
+        <v>217800</v>
+      </c>
+      <c r="C18" s="2">
+        <v>228049</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <v>3500</v>
+      </c>
+      <c r="B19" s="2">
+        <f t="shared" si="0"/>
+        <v>245000</v>
+      </c>
+      <c r="C19" s="2">
+        <v>255838</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>3700</v>
+      </c>
+      <c r="B20" s="2">
+        <f t="shared" si="0"/>
+        <v>273800</v>
+      </c>
+      <c r="C20" s="2">
+        <v>285391</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
+        <v>3900</v>
+      </c>
+      <c r="B21" s="2">
+        <f t="shared" si="0"/>
+        <v>304200</v>
+      </c>
+      <c r="C21" s="2">
+        <v>318014</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
+        <v>4100</v>
+      </c>
+      <c r="B22" s="2">
+        <f t="shared" si="0"/>
+        <v>336200</v>
+      </c>
+      <c r="C22" s="2">
+        <v>349271</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="2">
+        <v>4300</v>
+      </c>
+      <c r="B23" s="2">
+        <f t="shared" si="0"/>
+        <v>369800</v>
+      </c>
+      <c r="C23" s="2">
+        <v>383572</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
+        <v>4500</v>
+      </c>
+      <c r="B24" s="2">
+        <f t="shared" si="0"/>
+        <v>405000</v>
+      </c>
+      <c r="C24" s="2">
+        <v>419354</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="2">
+        <v>4700</v>
+      </c>
+      <c r="B25" s="2">
+        <f t="shared" si="0"/>
+        <v>441800</v>
+      </c>
+      <c r="C25" s="2">
+        <v>455017</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
+        <v>4900</v>
+      </c>
+      <c r="B26" s="2">
+        <f t="shared" si="0"/>
+        <v>480200</v>
+      </c>
+      <c r="C26" s="2">
+        <v>494703</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
+        <v>5100</v>
+      </c>
+      <c r="B27" s="2">
+        <f t="shared" si="0"/>
+        <v>520200</v>
+      </c>
+      <c r="C27" s="2">
+        <v>534469</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
+        <v>5300</v>
+      </c>
+      <c r="B28" s="2">
+        <f t="shared" si="0"/>
+        <v>561800</v>
+      </c>
+      <c r="C28" s="2">
+        <v>578279</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="2">
+        <v>5500</v>
+      </c>
+      <c r="B29" s="2">
+        <f t="shared" si="0"/>
+        <v>605000</v>
+      </c>
+      <c r="C29" s="2">
+        <v>621329</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
+        <v>5700</v>
+      </c>
+      <c r="B30" s="2">
+        <f t="shared" si="0"/>
+        <v>649800</v>
+      </c>
+      <c r="C30" s="2">
+        <v>665175</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
+        <v>5900</v>
+      </c>
+      <c r="B31" s="2">
+        <f t="shared" si="0"/>
+        <v>696200</v>
+      </c>
+      <c r="C31" s="2">
+        <v>712886</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
+        <v>6100</v>
+      </c>
+      <c r="B32" s="2">
+        <f t="shared" si="0"/>
+        <v>744200</v>
+      </c>
+      <c r="C32" s="2">
+        <v>759619</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
+        <v>6300</v>
+      </c>
+      <c r="B33" s="2">
+        <f t="shared" si="0"/>
+        <v>793800</v>
+      </c>
+      <c r="C33" s="2">
+        <v>812546</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
+        <v>6500</v>
+      </c>
+      <c r="B34" s="2">
+        <f t="shared" si="0"/>
+        <v>845000</v>
+      </c>
+      <c r="C34" s="2">
+        <v>863606</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="2">
+        <v>6700</v>
+      </c>
+      <c r="B35" s="2">
+        <f t="shared" si="0"/>
+        <v>897800</v>
+      </c>
+      <c r="C35" s="2">
+        <v>917533</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
+        <v>6900</v>
+      </c>
+      <c r="B36" s="2">
+        <f t="shared" si="0"/>
+        <v>952200</v>
+      </c>
+      <c r="C36" s="2">
+        <v>972079</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="2">
+        <v>7100</v>
+      </c>
+      <c r="B37" s="2">
+        <f t="shared" si="0"/>
+        <v>1008200</v>
+      </c>
+      <c r="C37" s="2">
+        <v>1027181</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="2">
+        <v>7300</v>
+      </c>
+      <c r="B38" s="2">
+        <f t="shared" si="0"/>
+        <v>1065800</v>
+      </c>
+      <c r="C38" s="2">
+        <v>1087236</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="2">
+        <v>7500</v>
+      </c>
+      <c r="B39" s="2">
+        <f t="shared" si="0"/>
+        <v>1125000</v>
+      </c>
+      <c r="C39" s="2">
+        <v>1149507</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="2">
+        <v>7700</v>
+      </c>
+      <c r="B40" s="2">
+        <f t="shared" si="0"/>
+        <v>1185800</v>
+      </c>
+      <c r="C40" s="2">
+        <v>1211949</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="2">
+        <v>7900</v>
+      </c>
+      <c r="B41" s="2">
+        <f t="shared" si="0"/>
+        <v>1248200</v>
+      </c>
+      <c r="C41" s="2">
+        <v>1271159</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="2">
+        <v>8100</v>
+      </c>
+      <c r="B42" s="2">
+        <f t="shared" si="0"/>
+        <v>1312200</v>
+      </c>
+      <c r="C42" s="2">
+        <v>1336629</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="2">
+        <v>8300</v>
+      </c>
+      <c r="B43" s="2">
+        <f t="shared" si="0"/>
+        <v>1377800</v>
+      </c>
+      <c r="C43" s="2">
+        <v>1402884</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="2">
+        <v>8500</v>
+      </c>
+      <c r="B44" s="2">
+        <f t="shared" si="0"/>
+        <v>1445000</v>
+      </c>
+      <c r="C44" s="2">
+        <v>1471282</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="2">
+        <v>8700</v>
+      </c>
+      <c r="B45" s="2">
+        <f t="shared" si="0"/>
+        <v>1513800</v>
+      </c>
+      <c r="C45" s="2">
+        <v>1542017</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="2">
+        <v>8900</v>
+      </c>
+      <c r="B46" s="2">
+        <f t="shared" si="0"/>
+        <v>1584200</v>
+      </c>
+      <c r="C46" s="2">
+        <v>1612898</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="2">
+        <v>9100</v>
+      </c>
+      <c r="B47" s="2">
+        <f t="shared" si="0"/>
+        <v>1656200</v>
+      </c>
+      <c r="C47" s="2">
+        <v>1684489</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="2">
+        <v>9300</v>
+      </c>
+      <c r="B48" s="2">
+        <f t="shared" si="0"/>
+        <v>1729800</v>
+      </c>
+      <c r="C48" s="2">
+        <v>1759271</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="2">
+        <v>9500</v>
+      </c>
+      <c r="B49" s="2">
+        <f t="shared" si="0"/>
+        <v>1805000</v>
+      </c>
+      <c r="C49" s="2">
+        <v>1833777</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="2">
+        <v>9700</v>
+      </c>
+      <c r="B50" s="2">
+        <f t="shared" si="0"/>
+        <v>1881800</v>
+      </c>
+      <c r="C50" s="2">
+        <v>1911227</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="2">
+        <v>9900</v>
+      </c>
+      <c r="B51" s="2">
+        <f t="shared" si="0"/>
+        <v>1960200</v>
+      </c>
+      <c r="C51" s="2">
+        <v>1991307</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>